--- a/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>ASFH</t>
   </si>
@@ -656,99 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -773,8 +780,14 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -782,17 +795,17 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,32 +824,38 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>400</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,14 +874,20 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,8 +904,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -923,8 +950,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,8 +1000,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1011,8 +1050,14 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1055,8 +1100,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,8 +1121,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1085,14 +1138,14 @@
         <v>800</v>
       </c>
       <c r="G17" s="3">
+        <v>700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>800</v>
+      </c>
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
         <v>0</v>
       </c>
@@ -1103,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3">
         <v>0</v>
@@ -1111,31 +1164,37 @@
       <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>200</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-100</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-300</v>
       </c>
       <c r="G18" s="3">
         <v>-100</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -1147,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3">
         <v>0</v>
@@ -1155,11 +1214,17 @@
       <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,8 +1241,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1217,31 +1284,37 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1253,19 +1326,25 @@
         <v>0</v>
       </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1308,29 +1387,35 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
@@ -1341,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3">
         <v>0</v>
@@ -1349,11 +1434,17 @@
       <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1361,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1393,11 +1484,17 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,29 +1537,35 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
@@ -1473,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
         <v>0</v>
@@ -1481,32 +1584,38 @@
       <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
@@ -1517,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
         <v>0</v>
@@ -1525,11 +1634,17 @@
       <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1687,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1737,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1787,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,8 +1837,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1745,32 +1884,38 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
@@ -1781,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3">
         <v>0</v>
@@ -1789,11 +1934,17 @@
       <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,29 +1987,35 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
@@ -1869,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
         <v>0</v>
@@ -1877,60 +2034,72 @@
       <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2116,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,34 +2136,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G41" s="3">
         <v>1300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1600</v>
-      </c>
-      <c r="G41" s="3">
-        <v>900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>900</v>
       </c>
       <c r="I41" s="3">
         <v>900</v>
       </c>
       <c r="J41" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="K41" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L41" s="3">
         <v>1000</v>
@@ -2001,33 +2174,39 @@
         <v>1000</v>
       </c>
       <c r="N41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -2053,37 +2232,43 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="F43" s="3">
         <v>500</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+        <v>600</v>
+      </c>
+      <c r="H43" s="3">
+        <v>500</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2094,11 +2279,17 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2141,37 +2332,43 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -2185,34 +2382,40 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F46" s="3">
         <v>2100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>900</v>
-      </c>
-      <c r="H46" s="3">
-        <v>900</v>
       </c>
       <c r="I46" s="3">
         <v>900</v>
       </c>
       <c r="J46" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="K46" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L46" s="3">
         <v>1000</v>
@@ -2221,16 +2424,22 @@
         <v>1000</v>
       </c>
       <c r="N46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P46" s="3">
         <v>400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>400</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2244,22 +2453,22 @@
         <v>400</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
+        <v>400</v>
+      </c>
+      <c r="H47" s="3">
+        <v>400</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2273,37 +2482,43 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>800</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2317,8 +2532,14 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2361,8 +2582,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2632,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,8 +2682,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2466,20 +2705,20 @@
       <c r="G52" s="3">
         <v>0</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2493,8 +2732,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,34 +2782,40 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F54" s="3">
         <v>2700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3400</v>
-      </c>
-      <c r="G54" s="3">
-        <v>900</v>
-      </c>
-      <c r="H54" s="3">
-        <v>900</v>
       </c>
       <c r="I54" s="3">
         <v>900</v>
       </c>
       <c r="J54" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="K54" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L54" s="3">
         <v>1000</v>
@@ -2573,16 +2824,22 @@
         <v>1000</v>
       </c>
       <c r="N54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P54" s="3">
         <v>400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>400</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2856,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,8 +2876,10 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2629,17 +2890,17 @@
         <v>0</v>
       </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
       <c r="J57" s="3">
         <v>0</v>
       </c>
@@ -2658,11 +2919,17 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2670,28 +2937,28 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
+        <v>200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>200</v>
+      </c>
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2705,40 +2972,46 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
+        <v>600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
       <c r="I59" s="3">
         <v>0</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3">
+        <v>0</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -2746,29 +3019,35 @@
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
         <v>900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
+        <v>900</v>
+      </c>
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
       </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
       <c r="I60" s="3">
         <v>0</v>
       </c>
@@ -2790,11 +3069,17 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2837,16 +3122,22 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -2854,20 +3145,20 @@
       <c r="G62" s="3">
         <v>0</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -2881,8 +3172,14 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3222,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3272,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,26 +3322,32 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="G66" s="3">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3">
-        <v>0</v>
-      </c>
       <c r="I66" s="3">
         <v>0</v>
       </c>
@@ -3054,11 +3369,17 @@
       <c r="O66" s="3">
         <v>0</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3396,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3442,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3492,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3207,8 +3542,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,28 +3592,34 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-8300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-8300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-8200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-600</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-500</v>
       </c>
       <c r="J72" s="3">
         <v>-500</v>
@@ -3281,22 +3628,28 @@
         <v>-500</v>
       </c>
       <c r="L72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N72" s="3">
         <v>-400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3692,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3742,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,34 +3792,40 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F76" s="3">
         <v>1800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2000</v>
-      </c>
-      <c r="G76" s="3">
-        <v>900</v>
-      </c>
-      <c r="H76" s="3">
-        <v>900</v>
       </c>
       <c r="I76" s="3">
         <v>900</v>
       </c>
       <c r="J76" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="K76" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L76" s="3">
         <v>1000</v>
@@ -3463,16 +3834,22 @@
         <v>1000</v>
       </c>
       <c r="N76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P76" s="3">
         <v>400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>400</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,78 +3892,90 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
@@ -3597,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N81" s="3">
         <v>0</v>
@@ -3605,11 +3994,17 @@
       <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,8 +4021,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3640,11 +4037,11 @@
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3652,11 +4049,11 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3670,8 +4067,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +4117,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +4167,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4217,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4267,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,26 +4317,32 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
@@ -3923,19 +4356,25 @@
         <v>0</v>
       </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,8 +4391,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3996,8 +4437,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4487,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,8 +4537,14 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4098,11 +4557,11 @@
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -4110,11 +4569,11 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -4128,8 +4587,14 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,8 +4611,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4158,14 +4625,14 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-400</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -4190,8 +4657,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4707,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4757,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,52 +4807,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4380,11 +4877,11 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -4392,11 +4889,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4410,26 +4907,32 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -4443,15 +4946,21 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>ASFH</t>
   </si>
@@ -656,88 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44530</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44439</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44347</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44255</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -745,20 +749,20 @@
         <v>500</v>
       </c>
       <c r="E8" s="3">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3">
         <v>1300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
@@ -786,13 +790,16 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -801,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="I9" s="3">
+        <v>100</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -830,35 +837,38 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -880,14 +890,17 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +919,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +970,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1023,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1056,8 +1076,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1106,8 +1129,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,8 +1149,9 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1132,23 +1159,23 @@
         <v>800</v>
       </c>
       <c r="E17" s="3">
+        <v>800</v>
+      </c>
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
       <c r="K17" s="3">
         <v>0</v>
       </c>
@@ -1162,19 +1189,22 @@
         <v>0</v>
       </c>
       <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
       <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1182,23 +1212,23 @@
         <v>-300</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>600</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-100</v>
       </c>
       <c r="G18" s="3">
         <v>-100</v>
       </c>
       <c r="H18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
         <v>0</v>
       </c>
@@ -1212,19 +1242,22 @@
         <v>0</v>
       </c>
       <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,8 +1276,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1290,11 +1324,14 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,22 +1339,22 @@
         <v>-300</v>
       </c>
       <c r="E21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F21" s="3">
         <v>600</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -1332,19 +1369,22 @@
         <v>0</v>
       </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1393,8 +1433,11 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1402,23 +1445,23 @@
         <v>-300</v>
       </c>
       <c r="E23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
         <v>0</v>
       </c>
@@ -1432,19 +1475,22 @@
         <v>0</v>
       </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1452,11 +1498,11 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1490,11 +1536,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,8 +1592,11 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1552,23 +1604,23 @@
         <v>-300</v>
       </c>
       <c r="E26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F26" s="3">
         <v>400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
         <v>0</v>
       </c>
@@ -1582,19 +1634,22 @@
         <v>0</v>
       </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1602,23 +1657,23 @@
         <v>-300</v>
       </c>
       <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
@@ -1632,19 +1687,22 @@
         <v>0</v>
       </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1804,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,8 +1910,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1890,11 +1960,14 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1902,23 +1975,23 @@
         <v>-300</v>
       </c>
       <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
         <v>0</v>
       </c>
@@ -1932,19 +2005,22 @@
         <v>0</v>
       </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,8 +2069,11 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2002,23 +2081,23 @@
         <v>-300</v>
       </c>
       <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
         <v>0</v>
       </c>
@@ -2032,74 +2111,80 @@
         <v>0</v>
       </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44530</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44439</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44347</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44255</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,28 +2224,29 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1300</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1200</v>
       </c>
       <c r="F41" s="3">
         <v>1200</v>
       </c>
       <c r="G41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H41" s="3">
         <v>1300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>900</v>
       </c>
       <c r="J41" s="3">
         <v>900</v>
@@ -2168,7 +2255,7 @@
         <v>900</v>
       </c>
       <c r="L41" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="M41" s="3">
         <v>1000</v>
@@ -2180,27 +2267,30 @@
         <v>1000</v>
       </c>
       <c r="P41" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="Q41" s="3">
         <v>400</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3">
+        <v>400</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -2208,8 +2298,8 @@
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2238,31 +2328,34 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E43" s="3">
+        <v>900</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>900</v>
+      </c>
+      <c r="I43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
-        <v>500</v>
-      </c>
-      <c r="G43" s="3">
-        <v>600</v>
-      </c>
-      <c r="H43" s="3">
-        <v>500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2270,8 +2363,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2285,11 +2378,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2338,40 +2434,43 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -2388,28 +2487,31 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2800</v>
-      </c>
-      <c r="I46" s="3">
-        <v>900</v>
       </c>
       <c r="J46" s="3">
         <v>900</v>
@@ -2418,7 +2520,7 @@
         <v>900</v>
       </c>
       <c r="L46" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="M46" s="3">
         <v>1000</v>
@@ -2430,16 +2532,19 @@
         <v>1000</v>
       </c>
       <c r="P46" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="Q46" s="3">
         <v>400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>400</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2459,10 +2564,10 @@
         <v>400</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2470,8 +2575,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2488,8 +2593,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2497,22 +2605,22 @@
         <v>700</v>
       </c>
       <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
         <v>800</v>
-      </c>
-      <c r="F48" s="3">
-        <v>200</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
       </c>
       <c r="H48" s="3">
+        <v>200</v>
+      </c>
+      <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="J48" s="3">
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2520,8 +2628,8 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2538,8 +2646,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2588,8 +2699,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2805,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2711,8 +2831,8 @@
       <c r="I52" s="3">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2720,8 +2840,8 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -2738,8 +2858,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,28 +2911,31 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E54" s="3">
         <v>3500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3400</v>
-      </c>
-      <c r="I54" s="3">
-        <v>900</v>
       </c>
       <c r="J54" s="3">
         <v>900</v>
@@ -2818,7 +2944,7 @@
         <v>900</v>
       </c>
       <c r="L54" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="M54" s="3">
         <v>1000</v>
@@ -2830,16 +2956,19 @@
         <v>1000</v>
       </c>
       <c r="P54" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="Q54" s="3">
         <v>400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3">
+        <v>400</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,13 +3008,14 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -2896,14 +3027,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
@@ -2925,11 +3056,14 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2943,16 +3077,16 @@
         <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2960,8 +3094,8 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2978,29 +3112,32 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
+        <v>700</v>
+      </c>
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
@@ -3010,11 +3147,11 @@
       <c r="L59" s="3">
         <v>0</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
@@ -3025,32 +3162,35 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1000</v>
-      </c>
-      <c r="E60" s="3">
-        <v>900</v>
       </c>
       <c r="F60" s="3">
         <v>900</v>
       </c>
       <c r="G60" s="3">
+        <v>900</v>
+      </c>
+      <c r="H60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
       <c r="J60" s="3">
         <v>0</v>
       </c>
@@ -3075,11 +3215,14 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3128,8 +3271,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3140,7 +3286,7 @@
         <v>600</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
@@ -3151,8 +3297,8 @@
       <c r="I62" s="3">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -3160,8 +3306,8 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -3178,8 +3324,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,29 +3483,32 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E66" s="3">
         <v>1500</v>
       </c>
       <c r="F66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G66" s="3">
         <v>900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1500</v>
       </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
       <c r="J66" s="3">
         <v>0</v>
       </c>
@@ -3375,11 +3533,14 @@
       <c r="Q66" s="3">
         <v>0</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3">
+        <v>0</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3663,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,31 +3769,34 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-8300</v>
       </c>
       <c r="G72" s="3">
         <v>-8300</v>
       </c>
       <c r="H72" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="I72" s="3">
         <v>-8200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-600</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-500</v>
       </c>
       <c r="K72" s="3">
         <v>-500</v>
@@ -3634,22 +3808,25 @@
         <v>-500</v>
       </c>
       <c r="N72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="O72" s="3">
         <v>-400</v>
       </c>
       <c r="P72" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,28 +3981,31 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>900</v>
       </c>
       <c r="J76" s="3">
         <v>900</v>
@@ -3828,7 +4014,7 @@
         <v>900</v>
       </c>
       <c r="L76" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="M76" s="3">
         <v>1000</v>
@@ -3840,16 +4026,19 @@
         <v>1000</v>
       </c>
       <c r="P76" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="Q76" s="3">
         <v>400</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3">
+        <v>400</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,63 +4087,69 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44530</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44439</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44347</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44255</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3962,23 +4157,23 @@
         <v>-300</v>
       </c>
       <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
@@ -3992,19 +4187,22 @@
         <v>0</v>
       </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4221,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4043,8 +4242,8 @@
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -4055,8 +4254,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4073,8 +4272,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,29 +4537,32 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>100</v>
       </c>
       <c r="F89" s="3">
+        <v>100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
@@ -4362,19 +4579,22 @@
         <v>0</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4613,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4443,8 +4664,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,8 +4770,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4563,8 +4793,8 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -4575,8 +4805,8 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -4593,8 +4823,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4846,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4631,11 +4865,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -4663,8 +4897,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,8 +5056,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4825,46 +5071,49 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4883,8 +5132,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -4895,8 +5144,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4913,29 +5162,32 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -4952,15 +5204,18 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>ASFH</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44530</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44439</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44347</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44255</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="3">
         <v>500</v>
       </c>
       <c r="F8" s="3">
+        <v>500</v>
+      </c>
+      <c r="G8" s="3">
         <v>1300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
@@ -793,17 +797,20 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
@@ -811,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="J9" s="3">
+        <v>100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -840,38 +847,41 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E10" s="3">
         <v>500</v>
       </c>
       <c r="F10" s="3">
+        <v>500</v>
+      </c>
+      <c r="G10" s="3">
         <v>1300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>700</v>
       </c>
-      <c r="H10" s="3">
-        <v>500</v>
-      </c>
       <c r="I10" s="3">
+        <v>600</v>
+      </c>
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -893,14 +903,17 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +933,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,8 +987,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,31 +1043,34 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1079,8 +1099,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,8 +1155,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,8 +1176,9 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1162,23 +1189,23 @@
         <v>800</v>
       </c>
       <c r="F17" s="3">
+        <v>800</v>
+      </c>
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
       <c r="L17" s="3">
         <v>0</v>
       </c>
@@ -1192,46 +1219,49 @@
         <v>0</v>
       </c>
       <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3">
         <v>-300</v>
       </c>
       <c r="F18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G18" s="3">
         <v>600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-100</v>
       </c>
       <c r="H18" s="3">
         <v>-100</v>
       </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
       <c r="L18" s="3">
         <v>0</v>
       </c>
@@ -1245,19 +1275,22 @@
         <v>0</v>
       </c>
       <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,8 +1310,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1300,8 +1334,8 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1327,37 +1361,40 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="E21" s="3">
         <v>-300</v>
       </c>
       <c r="F21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G21" s="3">
         <v>600</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
         <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
@@ -1372,42 +1409,45 @@
         <v>0</v>
       </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1436,35 +1476,38 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="E23" s="3">
         <v>-300</v>
       </c>
       <c r="F23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G23" s="3">
         <v>600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
         <v>0</v>
       </c>
@@ -1478,42 +1521,45 @@
         <v>0</v>
       </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1539,11 +1585,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,35 +1644,38 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="E26" s="3">
         <v>-300</v>
       </c>
       <c r="F26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G26" s="3">
         <v>400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
         <v>0</v>
       </c>
@@ -1637,46 +1689,49 @@
         <v>0</v>
       </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="E27" s="3">
         <v>-300</v>
       </c>
       <c r="F27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G27" s="3">
         <v>400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
         <v>0</v>
       </c>
@@ -1690,19 +1745,22 @@
         <v>0</v>
       </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1812,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1868,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1924,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,8 +1980,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1936,8 +2006,8 @@
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1963,38 +2033,41 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="E33" s="3">
         <v>-300</v>
       </c>
       <c r="F33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G33" s="3">
         <v>400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
         <v>0</v>
       </c>
@@ -2008,19 +2081,22 @@
         <v>0</v>
       </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,35 +2148,38 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="E35" s="3">
         <v>-300</v>
       </c>
       <c r="F35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G35" s="3">
         <v>400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
         <v>0</v>
       </c>
@@ -2114,77 +2193,83 @@
         <v>0</v>
       </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44530</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44439</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44347</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44255</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2289,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,31 +2311,32 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1200</v>
       </c>
       <c r="G41" s="3">
         <v>1200</v>
       </c>
       <c r="H41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1600</v>
-      </c>
-      <c r="J41" s="3">
-        <v>900</v>
       </c>
       <c r="K41" s="3">
         <v>900</v>
@@ -2258,7 +2345,7 @@
         <v>900</v>
       </c>
       <c r="M41" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="N41" s="3">
         <v>1000</v>
@@ -2270,36 +2357,39 @@
         <v>1000</v>
       </c>
       <c r="Q41" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>400</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2331,34 +2421,37 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
@@ -2366,8 +2459,8 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2381,34 +2474,37 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2437,8 +2533,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2452,28 +2551,28 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
@@ -2490,31 +2589,34 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2800</v>
-      </c>
-      <c r="J46" s="3">
-        <v>900</v>
       </c>
       <c r="K46" s="3">
         <v>900</v>
@@ -2523,7 +2625,7 @@
         <v>900</v>
       </c>
       <c r="M46" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="N46" s="3">
         <v>1000</v>
@@ -2535,42 +2637,45 @@
         <v>1000</v>
       </c>
       <c r="Q46" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="R46" s="3">
         <v>400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>400</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
+      <c r="K47" s="3">
+        <v>0</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
@@ -2578,8 +2683,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2596,34 +2701,37 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H48" s="3">
+        <v>600</v>
+      </c>
+      <c r="I48" s="3">
+        <v>600</v>
+      </c>
+      <c r="J48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
-        <v>700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
+      <c r="K48" s="3">
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
@@ -2631,8 +2739,8 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2649,8 +2757,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2702,8 +2813,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2869,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,34 +2925,37 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2843,8 +2963,8 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -2861,8 +2981,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,31 +3037,34 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3400</v>
-      </c>
-      <c r="J54" s="3">
-        <v>900</v>
       </c>
       <c r="K54" s="3">
         <v>900</v>
@@ -2947,7 +3073,7 @@
         <v>900</v>
       </c>
       <c r="M54" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="N54" s="3">
         <v>1000</v>
@@ -2959,16 +3085,19 @@
         <v>1000</v>
       </c>
       <c r="Q54" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="R54" s="3">
         <v>400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S54" s="3">
+        <v>400</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3117,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,17 +3139,18 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
       <c r="F57" s="3">
         <v>0</v>
       </c>
@@ -3030,14 +3161,14 @@
         <v>0</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -3059,11 +3190,14 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3071,25 +3205,25 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -3097,8 +3231,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3115,31 +3249,34 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
+        <v>600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>400</v>
+      </c>
+      <c r="H59" s="3">
+        <v>600</v>
+      </c>
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
-        <v>600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1100</v>
-      </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -3150,11 +3287,11 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -3165,11 +3302,14 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3177,23 +3317,23 @@
         <v>1100</v>
       </c>
       <c r="E60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F60" s="3">
         <v>1000</v>
-      </c>
-      <c r="F60" s="3">
-        <v>900</v>
       </c>
       <c r="G60" s="3">
         <v>900</v>
       </c>
       <c r="H60" s="3">
+        <v>900</v>
+      </c>
+      <c r="I60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
-        <v>0</v>
-      </c>
       <c r="K60" s="3">
         <v>0</v>
       </c>
@@ -3218,25 +3358,28 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -3274,34 +3417,37 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -3309,8 +3455,8 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -3327,8 +3473,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3529,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3585,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,32 +3641,35 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1600</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1500</v>
       </c>
       <c r="F66" s="3">
         <v>1500</v>
       </c>
       <c r="G66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H66" s="3">
         <v>900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1500</v>
       </c>
-      <c r="J66" s="3">
-        <v>0</v>
-      </c>
       <c r="K66" s="3">
         <v>0</v>
       </c>
@@ -3536,11 +3694,14 @@
       <c r="R66" s="3">
         <v>0</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S66" s="3">
+        <v>0</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3721,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3775,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3831,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +3887,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,34 +3943,37 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-8300</v>
       </c>
       <c r="H72" s="3">
         <v>-8300</v>
       </c>
       <c r="I72" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="J72" s="3">
         <v>-8200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-600</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-500</v>
       </c>
       <c r="L72" s="3">
         <v>-500</v>
@@ -3811,22 +3985,25 @@
         <v>-500</v>
       </c>
       <c r="O72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="P72" s="3">
         <v>-400</v>
       </c>
       <c r="Q72" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="R72" s="3">
         <v>-200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S72" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4055,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4111,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,31 +4167,34 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>900</v>
       </c>
       <c r="K76" s="3">
         <v>900</v>
@@ -4017,7 +4203,7 @@
         <v>900</v>
       </c>
       <c r="M76" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="N76" s="3">
         <v>1000</v>
@@ -4029,16 +4215,19 @@
         <v>1000</v>
       </c>
       <c r="Q76" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="R76" s="3">
         <v>400</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S76" s="3">
+        <v>400</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,93 +4279,99 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44530</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44439</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44347</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44255</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="E81" s="3">
         <v>-300</v>
       </c>
       <c r="F81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G81" s="3">
         <v>400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
@@ -4190,19 +4385,22 @@
         <v>0</v>
       </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4420,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4236,14 +4435,14 @@
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -4257,8 +4456,8 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -4275,8 +4474,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4530,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4586,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4642,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4698,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,32 +4754,35 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
-      </c>
-      <c r="E89" s="3">
-        <v>100</v>
       </c>
       <c r="F89" s="3">
         <v>100</v>
       </c>
       <c r="G89" s="3">
+        <v>100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>500</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
@@ -4582,19 +4799,22 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,8 +4834,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4667,8 +4888,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4944,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,8 +5000,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4796,8 +5026,8 @@
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -4808,8 +5038,8 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -4826,8 +5056,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,31 +5080,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-400</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4900,8 +5134,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5190,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5246,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,8 +5302,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5074,46 +5320,49 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5126,14 +5375,14 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -5147,8 +5396,8 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -5165,32 +5414,35 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
@@ -5207,15 +5459,18 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASFH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>ASFH</t>
   </si>
@@ -656,96 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44530</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>44439</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>44347</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>44255</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -753,32 +764,32 @@
         <v>1000</v>
       </c>
       <c r="E8" s="3">
+        <v>600</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>1300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -800,41 +811,50 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E9" s="3">
+        <v>600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
-        <v>100</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -850,47 +870,56 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G10" s="3">
         <v>1000</v>
       </c>
-      <c r="E10" s="3">
-        <v>500</v>
-      </c>
-      <c r="F10" s="3">
-        <v>500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1300</v>
-      </c>
       <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K10" s="3">
         <v>700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -906,14 +935,23 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,8 +972,11 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -990,8 +1031,17 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,8 +1096,17 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1072,14 +1131,14 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1102,8 +1161,17 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1158,8 +1226,17 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,44 +1254,47 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="3">
         <v>800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>700</v>
       </c>
       <c r="H17" s="3">
         <v>800</v>
       </c>
       <c r="I17" s="3">
+        <v>800</v>
+      </c>
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
+        <v>700</v>
+      </c>
+      <c r="M17" s="3">
+        <v>800</v>
+      </c>
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
@@ -1222,42 +1302,51 @@
         <v>0</v>
       </c>
       <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>300</v>
+      </c>
+      <c r="G18" s="3">
         <v>200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-300</v>
       </c>
       <c r="K18" s="3">
         <v>-100</v>
@@ -1266,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
@@ -1278,19 +1367,28 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,8 +1409,11 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1334,8 +1435,8 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1343,8 +1444,8 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1364,46 +1465,55 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>400</v>
+      </c>
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="J21" s="3">
         <v>600</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
-        <v>0</v>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O21" s="3">
         <v>0</v>
@@ -1412,19 +1522,28 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1449,14 +1568,14 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1479,31 +1598,40 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F23" s="3">
+        <v>300</v>
+      </c>
+      <c r="G23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-300</v>
       </c>
       <c r="K23" s="3">
         <v>-100</v>
@@ -1512,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O23" s="3">
         <v>0</v>
@@ -1524,19 +1652,28 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1546,20 +1683,20 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1567,8 +1704,8 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1588,11 +1725,20 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,31 +1793,40 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
+        <v>200</v>
+      </c>
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-300</v>
       </c>
       <c r="K26" s="3">
         <v>-100</v>
@@ -1680,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O26" s="3">
         <v>0</v>
@@ -1692,42 +1847,51 @@
         <v>0</v>
       </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
+        <v>200</v>
+      </c>
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="J27" s="3">
         <v>400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-300</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
@@ -1736,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O27" s="3">
         <v>0</v>
@@ -1748,19 +1912,28 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1988,17 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +2053,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +2118,17 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,8 +2183,17 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2006,8 +2215,8 @@
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2015,8 +2224,8 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2036,34 +2245,43 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
+        <v>200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-300</v>
       </c>
       <c r="K33" s="3">
         <v>-100</v>
@@ -2072,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
@@ -2084,19 +2302,28 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,31 +2378,40 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
+        <v>200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-300</v>
       </c>
       <c r="K35" s="3">
         <v>-100</v>
@@ -2184,10 +2420,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O35" s="3">
         <v>0</v>
@@ -2196,80 +2432,98 @@
         <v>0</v>
       </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44530</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>44439</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>44347</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>44255</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2544,11 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,22 +2569,25 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E41" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F41" s="3">
         <v>1300</v>
       </c>
       <c r="G41" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="H41" s="3">
         <v>1200</v>
@@ -2336,40 +2596,49 @@
         <v>1300</v>
       </c>
       <c r="J41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
-      </c>
-      <c r="N41" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O41" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P41" s="3">
-        <v>1000</v>
       </c>
       <c r="Q41" s="3">
         <v>1000</v>
       </c>
       <c r="R41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,22 +2693,31 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="E43" s="3">
-        <v>800</v>
-      </c>
-      <c r="F43" s="3">
-        <v>900</v>
-      </c>
       <c r="G43" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="H43" s="3">
         <v>800</v>
@@ -2448,28 +2726,28 @@
         <v>900</v>
       </c>
       <c r="J43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K43" s="3">
+        <v>800</v>
+      </c>
+      <c r="L43" s="3">
+        <v>900</v>
+      </c>
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2477,11 +2755,20 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2506,14 +2793,14 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2536,8 +2823,17 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2548,13 +2844,13 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
@@ -2563,25 +2859,25 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -2592,22 +2888,31 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G46" s="3">
         <v>2400</v>
-      </c>
-      <c r="E46" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F46" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>2600</v>
       </c>
       <c r="H46" s="3">
         <v>2100</v>
@@ -2616,40 +2921,49 @@
         <v>2300</v>
       </c>
       <c r="J46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M46" s="3">
         <v>2800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>900</v>
-      </c>
-      <c r="N46" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O46" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P46" s="3">
-        <v>1000</v>
       </c>
       <c r="Q46" s="3">
         <v>1000</v>
       </c>
       <c r="R46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U46" s="3">
         <v>400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="V46" s="3">
         <v>400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2657,17 +2971,17 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
       <c r="I47" s="3">
         <v>0</v>
       </c>
@@ -2677,23 +2991,23 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2704,52 +3018,61 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>700</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -2760,8 +3083,17 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2816,8 +3148,17 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +3213,17 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3278,17 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2954,8 +3313,8 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2963,17 +3322,17 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -2984,8 +3343,17 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,64 +3408,82 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F54" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G54" s="3">
         <v>3700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>3300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>3500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>3800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>2700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>2900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>3400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>900</v>
-      </c>
-      <c r="N54" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O54" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P54" s="3">
-        <v>1000</v>
       </c>
       <c r="Q54" s="3">
         <v>1000</v>
       </c>
       <c r="R54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U54" s="3">
         <v>400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3504,11 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,13 +3529,16 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
@@ -3158,26 +3550,26 @@
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>0</v>
       </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
@@ -3193,11 +3585,20 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3205,43 +3606,43 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>100</v>
       </c>
       <c r="J58" s="3">
+        <v>300</v>
+      </c>
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="L58" s="3">
+        <v>100</v>
+      </c>
+      <c r="M58" s="3">
+        <v>100</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3252,46 +3653,55 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
-        <v>400</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
       <c r="N59" s="3">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>0</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -3299,50 +3709,59 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>900</v>
       </c>
       <c r="I60" s="3">
         <v>1000</v>
       </c>
       <c r="J60" s="3">
+        <v>900</v>
+      </c>
+      <c r="K60" s="3">
+        <v>900</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M60" s="3">
         <v>1400</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3361,16 +3780,25 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
         <v>600</v>
@@ -3382,13 +3810,13 @@
         <v>600</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3420,8 +3848,17 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3446,8 +3883,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -3455,17 +3892,17 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -3476,8 +3913,17 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3978,17 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +4043,17 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,8 +4108,17 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3653,31 +4126,31 @@
         <v>1700</v>
       </c>
       <c r="E66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H66" s="3">
         <v>1600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>1500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H66" s="3">
-        <v>900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1000</v>
       </c>
       <c r="J66" s="3">
         <v>1500</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L66" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M66" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N66" s="3">
         <v>0</v>
@@ -3697,11 +4170,20 @@
       <c r="S66" s="3">
         <v>0</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T66" s="3">
+        <v>0</v>
+      </c>
+      <c r="U66" s="3">
+        <v>0</v>
+      </c>
+      <c r="V66" s="3">
+        <v>0</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +4204,11 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +4263,17 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +4328,17 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4393,17 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,64 +4458,82 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-8300</v>
+        <v>-8700</v>
       </c>
       <c r="E72" s="3">
         <v>-8500</v>
       </c>
       <c r="F72" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="I72" s="3">
         <v>-8200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>-7900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>-8300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>-8300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-8200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>-600</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-500</v>
       </c>
       <c r="O72" s="3">
         <v>-500</v>
       </c>
       <c r="P72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S72" s="3">
         <v>-400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>-400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>-200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="V72" s="3">
         <v>-200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4588,17 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4653,17 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,64 +4718,82 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G76" s="3">
         <v>2100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>1700</v>
-      </c>
-      <c r="F76" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H76" s="3">
-        <v>1800</v>
       </c>
       <c r="I76" s="3">
         <v>1900</v>
       </c>
       <c r="J76" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K76" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L76" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M76" s="3">
         <v>2000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>900</v>
-      </c>
-      <c r="N76" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O76" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P76" s="3">
-        <v>1000</v>
       </c>
       <c r="Q76" s="3">
         <v>1000</v>
       </c>
       <c r="R76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U76" s="3">
         <v>400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>400</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,92 +4848,110 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44530</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>44439</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>44347</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>44255</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
+        <v>200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-300</v>
       </c>
       <c r="K81" s="3">
         <v>-100</v>
@@ -4376,10 +4960,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O81" s="3">
         <v>0</v>
@@ -4388,19 +4972,28 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,8 +5014,11 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4435,14 +5031,14 @@
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -4459,14 +5055,14 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -4477,8 +5073,17 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +5138,17 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +5203,17 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +5268,17 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +5333,17 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,41 +5398,50 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>600</v>
+      </c>
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
@@ -4802,19 +5452,28 @@
         <v>0</v>
       </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,8 +5494,11 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4847,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -4891,8 +5553,17 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5618,17 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,8 +5683,17 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5015,7 +5704,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -5029,26 +5718,26 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -5059,8 +5748,17 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5779,11 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5104,18 +5805,18 @@
       <c r="I96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3">
         <v>400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5137,8 +5838,17 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5903,17 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5968,17 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,8 +6033,17 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5323,25 +6060,25 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -5349,20 +6086,29 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5375,14 +6121,14 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -5399,14 +6145,14 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -5417,40 +6163,49 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="E102" s="3">
         <v>-100</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G102" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="H102" s="3">
         <v>-100</v>
       </c>
       <c r="I102" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>100</v>
       </c>
       <c r="K102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L102" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="M102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -5462,15 +6217,24 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
